--- a/data/trans_camb/IP18_E_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18_E_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,99</t>
+          <t>-1,54; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,55</t>
+          <t>-5,84; 2,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 2,24</t>
+          <t>-28,88; 2,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,98</t>
+          <t>-1,69; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,89</t>
+          <t>-4,99; 1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,42</t>
+          <t>-1,15; 2,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,39</t>
+          <t>-3,59; 1,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 1,72</t>
+          <t>-10,63; 1,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,19</t>
+          <t>-1,55; 4,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,62</t>
+          <t>-5,93; 2,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 2,29</t>
+          <t>-29,29; 2,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,09</t>
+          <t>-1,69; 3,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1,94</t>
+          <t>-5,02; 1,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,52</t>
+          <t>-1,16; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,41</t>
+          <t>-3,62; 1,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1,75</t>
+          <t>-10,75; 1,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,87</t>
+          <t>-1,86; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,86</t>
+          <t>-1,78; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,25; -3,0</t>
+          <t>-24,48; -2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,94</t>
+          <t>-1,21; 3,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,59</t>
+          <t>-0,79; 3,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,52</t>
+          <t>-2,44; 4,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,37</t>
+          <t>-0,86; 2,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,62</t>
+          <t>-0,57; 2,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 0,31</t>
+          <t>-9,17; 0,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,07</t>
+          <t>-1,94; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,05</t>
+          <t>-1,84; 2,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,9; -3,1</t>
+          <t>-25,65; -3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,12</t>
+          <t>-1,26; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,81</t>
+          <t>-0,82; 3,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,81</t>
+          <t>-2,5; 4,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,5</t>
+          <t>-0,89; 2,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,78</t>
+          <t>-0,59; 2,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 0,33</t>
+          <t>-9,62; 0,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 8,59</t>
+          <t>-4,0; 8,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,49</t>
+          <t>-5,61; 7,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 2,8</t>
+          <t>-23,92; 1,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 11,9</t>
+          <t>-0,51; 12,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 9,85</t>
+          <t>-3,08; 9,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 11,08</t>
+          <t>-16,54; 9,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,03</t>
+          <t>-0,93; 8,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,12</t>
+          <t>-2,66; 6,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 5,07</t>
+          <t>-16,19; 3,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 10,29</t>
+          <t>-4,47; 10,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 7,63</t>
+          <t>-6,3; 8,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 3,29</t>
+          <t>-26,77; 1,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 15,11</t>
+          <t>-0,59; 15,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 12,72</t>
+          <t>-3,6; 12,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 13,52</t>
+          <t>-19,58; 12,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,63</t>
+          <t>-1,04; 10,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 7,39</t>
+          <t>-3,0; 7,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 6,12</t>
+          <t>-18,74; 4,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,47</t>
+          <t>-1,15; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,89</t>
+          <t>-1,78; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,39; -3,99</t>
+          <t>-20,09; -3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,73</t>
+          <t>-0,55; 3,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,09</t>
+          <t>-0,88; 3,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,23</t>
+          <t>-3,74; 4,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,8</t>
+          <t>-0,13; 3,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,22</t>
+          <t>-0,68; 2,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -0,37</t>
+          <t>-8,48; -0,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,82</t>
+          <t>-1,21; 3,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,16</t>
+          <t>-1,89; 2,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -4,32</t>
+          <t>-21,28; -3,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,06</t>
+          <t>-0,58; 3,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,35</t>
+          <t>-0,93; 3,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,61</t>
+          <t>-3,99; 4,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,03</t>
+          <t>-0,14; 3,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,4</t>
+          <t>-0,73; 2,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; -0,39</t>
+          <t>-9,04; -0,35</t>
         </is>
       </c>
     </row>
